--- a/admin.xlsx
+++ b/admin.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9dc092c295d87c3b/Desktop/testing/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9dc092c295d87c3b/Desktop/wealth wise vishal website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="11_F25DC773A252ABDACC10480EA1DB6DB85ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC1219A6-A610-45A7-B716-55A05B45F187}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="11_F25DC773A252ABDACC10480EA1DB6DB85ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD54120C-6B01-47A7-B78C-9446CFBF52AB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -557,7 +557,7 @@
         <v>15</v>
       </c>
       <c r="G4">
-        <v>13000</v>
+        <v>12000</v>
       </c>
       <c r="H4">
         <v>11230</v>

--- a/admin.xlsx
+++ b/admin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9dc092c295d87c3b/Desktop/wealth wise vishal website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="11_F25DC773A252ABDACC10480EA1DB6DB85ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD54120C-6B01-47A7-B78C-9446CFBF52AB}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="11_F25DC773A252ABDACC10480EA1DB6DB85ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F60D1040-05B4-4E7C-A696-C1038AA087CE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -557,7 +557,7 @@
         <v>15</v>
       </c>
       <c r="G4">
-        <v>12000</v>
+        <v>11000</v>
       </c>
       <c r="H4">
         <v>11230</v>

--- a/admin.xlsx
+++ b/admin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9dc092c295d87c3b/Desktop/wealth wise vishal website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="11_F25DC773A252ABDACC10480EA1DB6DB85ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F60D1040-05B4-4E7C-A696-C1038AA087CE}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="11_F25DC773A252ABDACC10480EA1DB6DB85ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A64D55B8-0DF4-41F6-8F35-459875F4EFB7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
   <si>
     <t xml:space="preserve">stock name </t>
   </si>
@@ -118,13 +118,28 @@
   </si>
   <si>
     <t>https://news-images.dhan.co/irfc-posts-record-h1-fy27-net-profit-3-885-69-crore-up-10-31.jpg</t>
+  </si>
+  <si>
+    <t>https://assets.upstox.com/content/assets/images/news/meesho.webp</t>
+  </si>
+  <si>
+    <t>https://images.dhan.co/symbol/MEESHO.png</t>
+  </si>
+  <si>
+    <t>Meesho Day 1 orders grow 75% YoY as festive demand peaks</t>
+  </si>
+  <si>
+    <t>Transacting customers increased by ~60% YoY, driven by strong uptake in Fashion, Home &amp; Kitchen, Beauty &amp; Personal Care, Kids, and Electronic Accessories. The surge underscores the platform's expanding reach as it captures broader consumer participation during the festive season.</t>
+  </si>
+  <si>
+    <t>Meesho</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -136,6 +151,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -158,18 +181,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -448,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.140625" bestFit="1" customWidth="1"/>
@@ -501,7 +527,7 @@
       <c r="E2" t="s">
         <v>20</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="4" t="s">
         <v>21</v>
       </c>
       <c r="G2">
@@ -589,8 +615,31 @@
         <v>72</v>
       </c>
     </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" t="s">
+        <v>31</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{BE7248C2-FB5C-4810-A38C-D73A7572B623}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
--- a/admin.xlsx
+++ b/admin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9dc092c295d87c3b/Desktop/wealth wise vishal website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_2516FA94EBE1C3DFF76692F4166B26C02BB1A2F5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15E64937-1A38-4239-AC0B-12A121BF79C3}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_2516FA94EBE1C3DFF76692F4166B26C02BB1A2F5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27BB811F-A3D3-4678-8553-D5D454C3C3B0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>stock name</t>
   </si>
@@ -46,9 +46,6 @@
     <t>closing</t>
   </si>
   <si>
-    <t>RELIANCE</t>
-  </si>
-  <si>
     <t>DRREDDY</t>
   </si>
   <si>
@@ -116,13 +113,90 @@
   </si>
   <si>
     <t>https://images.dhan.co/symbol/WOCKPHARMA.png</t>
+  </si>
+  <si>
+    <t>GLENMARK</t>
+  </si>
+  <si>
+    <t>E2E Networks Ltd</t>
+  </si>
+  <si>
+    <t>E2E</t>
+  </si>
+  <si>
+    <t>E2E Networks proposes to expand capacity by around 5.4 MW for NVIDIA HGX B300 systems and other GPUs</t>
+  </si>
+  <si>
+    <t>https://images.cnbctv18.com/uploads/2026/02/image-2026-02-9601da6216aa984cdbf0fc901b99bf59.jpg?impolicy=website&amp;width=416&amp;height=234</t>
+  </si>
+  <si>
+    <t>E2E Networks on Monday, October 26, said it has proposed to expand its capacity by approximately 5.4 mega watt (MW) for NVIDIA HGX B300 systems and other graphic processing units (GPUs).
+The company, in an exchange filing, said this will take its total capacity to around 14.6 MW if the expansion is implemented in full.
+It said the proposed addition would build on its existing capacity of approximately 9.2 MW, which is being used to provide GPU cloud infrastructure and other artificial intelligence (AI)-related services.</t>
+  </si>
+  <si>
+    <t>https://images.dhan.co/symbol/E2E.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://images.dhan.co/symbol/APARINDS.png </t>
+  </si>
+  <si>
+    <t>Apar Industries</t>
+  </si>
+  <si>
+    <t>Apar Industries shareholders approve all AGM resolutions with minor dissent</t>
+  </si>
+  <si>
+    <t>The meeting, conducted via video conferencing, saw the adoption of audited financial statements for FY26 and the reappointment of Mr. Chaitanya N. Desai as director by rotation. While the dividend and financial statements received near-unanimous support, the director's reappointment saw 2.94% of votes cast against it, primarily from institutional investors.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://news-images.dhan.co/apar-industries-approves-60-dividend-per-share-37th-agm.jpg </t>
+  </si>
+  <si>
+    <t>APARINDS</t>
+  </si>
+  <si>
+    <t>Dollex Agrotech board approves renewable energy subsidiary</t>
+  </si>
+  <si>
+    <t>DOLLEX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://news-images.dhan.co/dollex-agrotech-board-approves-renewable-energy-subsidiary.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://images.dhan.co/symbol/DOLLEX.png </t>
+  </si>
+  <si>
+    <t>Dollex Agrotech Limited board has approved the incorporation of a wholly owned subsidiary, Dollex Green Ventures Pvt. Ltd., to operate in the renewable energy sector. The move marks the company's strategic entry into biogas, bioenergy, and organic fertilizer markets.</t>
+  </si>
+  <si>
+    <t>Dollex Agrotech Ltd</t>
+  </si>
+  <si>
+    <t>Permanent Magnets</t>
+  </si>
+  <si>
+    <t>PERMAGN</t>
+  </si>
+  <si>
+    <t>Permanent Magnets Q2FY27 Results: Net profit up 156% YoY; results published</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://news-images.dhan.co/permanent-magnets-net-profit-up-156-yoy-q2fy27.jpg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://images.dhan.co/symbol/PERMAGN.png </t>
+  </si>
+  <si>
+    <t>Permanent Magnets reported a 156% year-on-year increase in standalone net profit to ₹9.98 crore for the quarter ended September 30, 2026. Revenue from operations rose 49% to ₹72.46 crore, supported by robust demand in the electric vehicle (EV) segment and smart meter applications.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -160,6 +234,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF4F4F4F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -178,10 +265,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -199,8 +287,15 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -421,7 +516,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.85546875" style="7" customWidth="1"/>
@@ -459,93 +554,198 @@
     </row>
     <row r="2" spans="1:8" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>14</v>
+      <c r="G2">
+        <v>1253</v>
+      </c>
+      <c r="H2" s="9">
+        <v>1310.9</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>17</v>
+      <c r="G3">
+        <v>1961</v>
+      </c>
+      <c r="H3" s="9">
+        <v>2058.9</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="6" t="s">
+      <c r="D4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="E4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>25</v>
+      <c r="G4">
+        <v>2134</v>
+      </c>
+      <c r="H4" s="9">
+        <v>2225.8000000000002</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="E5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="6"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
+      <c r="G5">
+        <v>1800</v>
+      </c>
+      <c r="H5" s="9">
+        <v>1808</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="165.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>53</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E7" r:id="rId1" xr:uid="{429CC4DD-5250-49B9-A259-A6FF369E477A}"/>
+    <hyperlink ref="F7" r:id="rId2" xr:uid="{FBED335E-76E3-4C2F-8B75-CF79323630F2}"/>
+    <hyperlink ref="F8" r:id="rId3" xr:uid="{A157F54E-8E6B-4A37-A758-007DDC04CFF8}"/>
+    <hyperlink ref="E8" r:id="rId4" xr:uid="{0F6B0A62-61D3-4993-8877-717E16471ACB}"/>
+    <hyperlink ref="F9" r:id="rId5" xr:uid="{0ED5A2C9-8597-4D2A-9FF8-104EBB35FC1F}"/>
+    <hyperlink ref="E9" r:id="rId6" xr:uid="{AE45FFC0-FE7A-47C8-A199-C49DBEC9B53C}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>